--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="21">
   <si>
     <t>#</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>Max</t>
+  </si>
+  <si>
+    <t>RateNumber</t>
   </si>
   <si>
     <t>Number</t>
@@ -153,6 +156,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
@@ -164,13 +174,6 @@
       <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -782,19 +785,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1114,142 +1118,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N97"/>
+  <dimension ref="C1:O96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="18.4166666666667" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.5" style="1" customWidth="1"/>
     <col min="7" max="8" width="12.25" style="1" customWidth="1"/>
-    <col min="9" max="12" width="11.125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="23.125" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="9" max="13" width="11.125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="23.125" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:14">
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" customHeight="1" spans="3:15">
       <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:14">
-      <c r="M2" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>0</v>
       </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:15">
       <c r="N2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="M3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C5" s="3" t="s">
+      <c r="M4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
         <v>100</v>
@@ -1267,50 +1280,55 @@
         <v>100</v>
       </c>
       <c r="L6" s="1">
+        <v>10</v>
+      </c>
+      <c r="M6" s="1">
         <v>2</v>
       </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1">
+      <c r="N6" s="1"/>
+      <c r="O6" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
+    <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="3:15">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="4">
-        <v>2</v>
+      <c r="E7" s="1">
+        <v>30001</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1">
         <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L7" s="1">
-        <v>4</v>
-      </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1318,34 +1336,38 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>30001</v>
+        <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>50</v>
+      </c>
+      <c r="I8" s="1">
         <v>100</v>
       </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>10</v>
       </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
       <c r="K8" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L8" s="1">
-        <v>1</v>
-      </c>
-      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1353,35 +1375,38 @@
         <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H9" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1">
         <v>100</v>
       </c>
       <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1">
         <v>10</v>
       </c>
-      <c r="K9" s="1">
-        <v>1</v>
-      </c>
-      <c r="L9" s="1">
-        <v>1</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1">
+      <c r="M9" s="1">
+        <v>2</v>
+      </c>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1389,10 +1414,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="G10" s="1">
         <v>20</v>
@@ -1407,17 +1432,16 @@
         <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L10" s="1">
-        <v>2</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>10</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="3:15">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1425,16 +1449,16 @@
         <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>5</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>17</v>
+        <v>6</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="G11" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H11" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I11" s="1">
         <v>100</v>
@@ -1443,13 +1467,16 @@
         <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
+        <v>20</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:15">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1457,395 +1484,379 @@
         <v>1</v>
       </c>
       <c r="E12" s="1">
-        <v>6</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>18</v>
+        <v>7</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="G12" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H12" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I12" s="1">
         <v>100</v>
       </c>
       <c r="J12" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K12" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:14">
-      <c r="C13" s="1">
-        <v>8</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
-        <v>7</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="1">
-        <v>5</v>
-      </c>
-      <c r="H13" s="1">
-        <v>30</v>
-      </c>
-      <c r="I13" s="1">
-        <v>100</v>
-      </c>
-      <c r="J13" s="1">
-        <v>5</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
-      <c r="E16" s="4"/>
-    </row>
-    <row r="22" customHeight="1" spans="3:14">
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" customHeight="1" spans="3:14">
-      <c r="E23" s="6"/>
-    </row>
-    <row r="24" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
-      <c r="E26" s="4"/>
-    </row>
-    <row r="32" customHeight="1" spans="3:14">
-      <c r="E32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="3:12">
-      <c r="E33" s="6"/>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="E35" s="4"/>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="E36" s="4"/>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="E37" s="7"/>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="E38" s="7"/>
-    </row>
-    <row r="39" customHeight="1" spans="3:12">
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" customHeight="1" spans="3:12">
-      <c r="E40" s="7"/>
-    </row>
-    <row r="41" customHeight="1" spans="3:12">
-      <c r="E41" s="7"/>
-    </row>
-    <row r="42" customHeight="1" spans="3:12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="20" customHeight="1" spans="3:15">
+      <c r="E15" s="5"/>
+    </row>
+    <row r="21" customHeight="1" spans="3:15">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" customHeight="1" spans="3:15">
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="20" customHeight="1" spans="3:15">
+      <c r="E25" s="5"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:15">
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" customHeight="1" spans="3:15">
+      <c r="E32" s="7"/>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="E34" s="5"/>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+      <c r="E35" s="5"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="E36" s="8"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="E37" s="8"/>
+    </row>
+    <row r="38" customHeight="1" spans="3:13">
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" customHeight="1" spans="3:13">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" customHeight="1" spans="3:13">
+      <c r="E40" s="8"/>
+    </row>
+    <row r="41" customHeight="1" spans="3:13">
+      <c r="E41" s="8"/>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
       <c r="E42" s="7"/>
     </row>
-    <row r="43" customHeight="1" spans="3:12">
-      <c r="E43" s="6"/>
-    </row>
-    <row r="44" customHeight="1" spans="3:12">
-      <c r="E44" s="6"/>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="43" customHeight="1" spans="3:13">
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+    </row>
+    <row r="45" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C45" s="1"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="M45" s="1"/>
+    </row>
+    <row r="46" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="1"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="1"/>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C47" s="1"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="1"/>
-    </row>
-    <row r="49" customHeight="1" spans="5:14">
-      <c r="E49" s="4"/>
-    </row>
-    <row r="50" customHeight="1" spans="5:14">
-      <c r="E50" s="4"/>
-    </row>
-    <row r="51" customHeight="1" spans="5:14">
-      <c r="E51" s="7"/>
-    </row>
-    <row r="52" customHeight="1" spans="5:14">
-      <c r="E52" s="7"/>
-    </row>
-    <row r="53" customHeight="1" spans="5:14">
-      <c r="E53" s="2"/>
-    </row>
-    <row r="54" customHeight="1" spans="5:14">
-      <c r="E54" s="7"/>
-    </row>
-    <row r="55" customHeight="1" spans="5:14">
-      <c r="E55" s="7"/>
-    </row>
-    <row r="56" customHeight="1" spans="5:14">
+      <c r="D46" s="3"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="M46" s="1"/>
+    </row>
+    <row r="48" customHeight="1" spans="3:13">
+      <c r="E48" s="5"/>
+    </row>
+    <row r="49" customHeight="1" spans="5:15">
+      <c r="E49" s="5"/>
+    </row>
+    <row r="50" customHeight="1" spans="5:15">
+      <c r="E50" s="8"/>
+    </row>
+    <row r="51" customHeight="1" spans="5:15">
+      <c r="E51" s="8"/>
+    </row>
+    <row r="52" customHeight="1" spans="5:15">
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" customHeight="1" spans="5:15">
+      <c r="E53" s="8"/>
+    </row>
+    <row r="54" customHeight="1" spans="5:15">
+      <c r="E54" s="8"/>
+    </row>
+    <row r="55" customHeight="1" spans="5:15">
+      <c r="E55" s="8"/>
+    </row>
+    <row r="56" customHeight="1" spans="5:15">
       <c r="E56" s="7"/>
     </row>
-    <row r="57" customHeight="1" spans="5:14">
-      <c r="E57" s="6"/>
-    </row>
-    <row r="58" customHeight="1" spans="5:14">
-      <c r="E58" s="6"/>
-    </row>
-    <row r="59" customHeight="1" spans="5:14">
-      <c r="E59" s="4"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-    </row>
-    <row r="60" customHeight="1" spans="5:14">
-      <c r="E60" s="7"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-      <c r="M60" s="2"/>
-      <c r="N60" s="2"/>
-    </row>
-    <row r="61" customHeight="1" spans="5:14">
-      <c r="E61" s="4"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-      <c r="M61" s="2"/>
-      <c r="N61" s="2"/>
-    </row>
-    <row r="62" customHeight="1" spans="5:14">
-      <c r="E62" s="4"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-      <c r="M62" s="2"/>
-      <c r="N62" s="2"/>
-    </row>
-    <row r="63" customHeight="1" spans="5:14">
-      <c r="E63" s="4"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
-    </row>
-    <row r="64" customHeight="1" spans="5:14">
-      <c r="E64" s="7"/>
-    </row>
-    <row r="65" customHeight="1" spans="5:14">
-      <c r="E65" s="4"/>
-    </row>
-    <row r="66" customHeight="1" spans="5:14">
-      <c r="E66" s="4"/>
-    </row>
-    <row r="67" customHeight="1" spans="5:14">
-      <c r="E67" s="7"/>
-    </row>
-    <row r="68" customHeight="1" spans="5:14">
-      <c r="E68" s="7"/>
-    </row>
-    <row r="69" customHeight="1" spans="5:14">
-      <c r="E69" s="2"/>
-    </row>
-    <row r="70" customHeight="1" spans="5:14">
-      <c r="E70" s="7"/>
-    </row>
-    <row r="71" customHeight="1" spans="5:14">
-      <c r="E71" s="7"/>
-    </row>
-    <row r="72" customHeight="1" spans="5:14">
+    <row r="57" customHeight="1" spans="5:15">
+      <c r="E57" s="7"/>
+    </row>
+    <row r="58" customHeight="1" spans="5:15">
+      <c r="E58" s="5"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+    </row>
+    <row r="59" customHeight="1" spans="5:15">
+      <c r="E59" s="8"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" customHeight="1" spans="5:15">
+      <c r="E60" s="5"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" customHeight="1" spans="5:15">
+      <c r="E61" s="5"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" customHeight="1" spans="5:15">
+      <c r="E62" s="5"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" customHeight="1" spans="5:15">
+      <c r="E63" s="8"/>
+    </row>
+    <row r="64" customHeight="1" spans="5:15">
+      <c r="E64" s="5"/>
+    </row>
+    <row r="65" customHeight="1" spans="5:15">
+      <c r="E65" s="5"/>
+    </row>
+    <row r="66" customHeight="1" spans="5:15">
+      <c r="E66" s="8"/>
+    </row>
+    <row r="67" customHeight="1" spans="5:15">
+      <c r="E67" s="8"/>
+    </row>
+    <row r="68" customHeight="1" spans="5:15">
+      <c r="E68" s="3"/>
+    </row>
+    <row r="69" customHeight="1" spans="5:15">
+      <c r="E69" s="8"/>
+    </row>
+    <row r="70" customHeight="1" spans="5:15">
+      <c r="E70" s="8"/>
+    </row>
+    <row r="71" customHeight="1" spans="5:15">
+      <c r="E71" s="8"/>
+    </row>
+    <row r="72" customHeight="1" spans="5:15">
       <c r="E72" s="7"/>
     </row>
-    <row r="73" customHeight="1" spans="5:14">
-      <c r="E73" s="6"/>
-    </row>
-    <row r="74" customHeight="1" spans="5:14">
-      <c r="E74" s="6"/>
-    </row>
-    <row r="75" customHeight="1" spans="5:14">
-      <c r="E75" s="4"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-    </row>
-    <row r="76" customHeight="1" spans="5:14">
-      <c r="E76" s="7"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
-    </row>
-    <row r="77" customHeight="1" spans="5:14">
-      <c r="E77" s="4"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-    </row>
-    <row r="78" customHeight="1" spans="5:14">
-      <c r="E78" s="4"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-    </row>
-    <row r="79" customHeight="1" spans="5:14">
-      <c r="E79" s="4"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
-    </row>
-    <row r="82" customHeight="1" spans="5:14">
-      <c r="E82" s="4"/>
-    </row>
-    <row r="83" customHeight="1" spans="5:14">
-      <c r="E83" s="4"/>
-    </row>
-    <row r="84" customHeight="1" spans="5:14">
-      <c r="E84" s="4"/>
-    </row>
-    <row r="85" customHeight="1" spans="5:14">
-      <c r="E85" s="7"/>
-    </row>
-    <row r="86" customHeight="1" spans="5:14">
-      <c r="E86" s="7"/>
-    </row>
-    <row r="87" customHeight="1" spans="5:14">
-      <c r="E87" s="2"/>
-    </row>
-    <row r="88" customHeight="1" spans="5:14">
-      <c r="E88" s="7"/>
-    </row>
-    <row r="89" customHeight="1" spans="5:14">
-      <c r="E89" s="7"/>
-    </row>
-    <row r="90" customHeight="1" spans="5:14">
+    <row r="73" customHeight="1" spans="5:15">
+      <c r="E73" s="7"/>
+    </row>
+    <row r="74" customHeight="1" spans="5:15">
+      <c r="E74" s="5"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+    </row>
+    <row r="75" customHeight="1" spans="5:15">
+      <c r="E75" s="8"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" customHeight="1" spans="5:15">
+      <c r="E76" s="5"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" customHeight="1" spans="5:15">
+      <c r="E77" s="5"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="78" customHeight="1" spans="5:15">
+      <c r="E78" s="5"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+    </row>
+    <row r="81" customHeight="1" spans="5:15">
+      <c r="E81" s="5"/>
+    </row>
+    <row r="82" customHeight="1" spans="5:15">
+      <c r="E82" s="5"/>
+    </row>
+    <row r="83" customHeight="1" spans="5:15">
+      <c r="E83" s="5"/>
+    </row>
+    <row r="84" customHeight="1" spans="5:15">
+      <c r="E84" s="8"/>
+    </row>
+    <row r="85" customHeight="1" spans="5:15">
+      <c r="E85" s="8"/>
+    </row>
+    <row r="86" customHeight="1" spans="5:15">
+      <c r="E86" s="3"/>
+    </row>
+    <row r="87" customHeight="1" spans="5:15">
+      <c r="E87" s="8"/>
+    </row>
+    <row r="88" customHeight="1" spans="5:15">
+      <c r="E88" s="8"/>
+    </row>
+    <row r="89" customHeight="1" spans="5:15">
+      <c r="E89" s="8"/>
+    </row>
+    <row r="90" customHeight="1" spans="5:15">
       <c r="E90" s="7"/>
     </row>
-    <row r="91" customHeight="1" spans="5:14">
-      <c r="E91" s="6"/>
-    </row>
-    <row r="92" customHeight="1" spans="5:14">
-      <c r="E92" s="6"/>
-    </row>
-    <row r="93" customHeight="1" spans="5:14">
-      <c r="E93" s="4"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-    </row>
-    <row r="94" customHeight="1" spans="5:14">
-      <c r="E94" s="7"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
-      <c r="M94" s="2"/>
-      <c r="N94" s="2"/>
-    </row>
-    <row r="95" customHeight="1" spans="5:14">
-      <c r="E95" s="4"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
-      <c r="M95" s="2"/>
-      <c r="N95" s="2"/>
-    </row>
-    <row r="96" customHeight="1" spans="5:14">
-      <c r="E96" s="4"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
-      <c r="M96" s="2"/>
-      <c r="N96" s="2"/>
-    </row>
-    <row r="97" customHeight="1" spans="5:14">
-      <c r="E97" s="4"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
-      <c r="M97" s="2"/>
-      <c r="N97" s="2"/>
+    <row r="91" customHeight="1" spans="5:15">
+      <c r="E91" s="7"/>
+    </row>
+    <row r="92" customHeight="1" spans="5:15">
+      <c r="E92" s="5"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+    </row>
+    <row r="93" customHeight="1" spans="5:15">
+      <c r="E93" s="8"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3"/>
+      <c r="N93" s="3"/>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" customHeight="1" spans="5:15">
+      <c r="E94" s="5"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" customHeight="1" spans="5:15">
+      <c r="E95" s="5"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" customHeight="1" spans="5:15">
+      <c r="E96" s="5"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
